--- a/Estoque Almox/requisição.xlsx
+++ b/Estoque Almox/requisição.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proce\OneDrive\Área de Trabalho\PROJETOS\Requisicao-compras\Estoque Almox\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B16312F-A748-48D5-9A81-FB1684E7D816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Plan1"/>
+    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Plan1!$A$1:$D$50</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="115">
   <si>
     <t>Gr</t>
   </si>
@@ -31,158 +37,343 @@
     <t>Descricao do Material</t>
   </si>
   <si>
-    <t>METAL CLEAN FE-05 (DES.MULTICLEANER MOR)</t>
-  </si>
-  <si>
-    <t>SULFATO DE NIQUEL SOLUﾇﾃO</t>
-  </si>
-  <si>
-    <t>METAL CLEAN 7E - F ( CROMACAO )</t>
-  </si>
-  <si>
-    <t>STRIP COAT UNIQUE</t>
-  </si>
-  <si>
-    <t>ENVIROCOPPER MAKE UP</t>
-  </si>
-  <si>
-    <t>SUPRESSOR CRMC/H</t>
-  </si>
-  <si>
-    <t>COMPOSTO CRMC ONU:3085,5.1</t>
-  </si>
-  <si>
-    <t>ENVIROCOPPER BRIGHTNER</t>
-  </si>
-  <si>
-    <t>BROCA AﾇO RAPIDO 05,0MM</t>
-  </si>
-  <si>
-    <t>BROCA AﾇO RAPIDO 10,0MM</t>
-  </si>
-  <si>
-    <t>REB.WIDEA ART.FE.39C.100K-6ｨX3/4ｨX1.1/4</t>
-  </si>
-  <si>
-    <t>BROCA ACO RAPIDO 06,7MM</t>
-  </si>
-  <si>
-    <t>CHAVE SOQUETE PONTA HEXAGONAL 4MM ENCAIXE 1/4 R42</t>
-  </si>
-  <si>
-    <t>SERRA COPO DIAMANTADA DIAM. 35MM HASTE SEXT. 10MM</t>
-  </si>
-  <si>
-    <t>CAIXA 1623 (ARTE 2018)</t>
-  </si>
-  <si>
-    <t>BERCO ACESSORIO 509</t>
-  </si>
-  <si>
-    <t>CAIXA 1623-1 (ARTE 2018)</t>
-  </si>
-  <si>
-    <t>CAIXA 191 (ARTE 2018)</t>
-  </si>
-  <si>
-    <t>CAIXA 189-1 ( ARTE 2018)</t>
-  </si>
-  <si>
-    <t>VERG. RED. 3/8 (9,52MM)</t>
-  </si>
-  <si>
-    <t>VERG. SEXT. 9/16ｨ(14,28MM)</t>
-  </si>
-  <si>
-    <t>VERG. RED. 5/16ｨ( 7,94MM)</t>
-  </si>
-  <si>
-    <t>VERG. RED. 1.1/2ｨ (38,10MM)</t>
-  </si>
-  <si>
-    <t>VERG. QUAD. 1/2ｨ (12,7MM) - MEIO DURO</t>
-  </si>
-  <si>
-    <t>VERG. RED. 1.1/8ｴｴ (28,57MM)</t>
-  </si>
-  <si>
-    <t>VERG. QUAD. 1ｨ (25,40MM)</t>
-  </si>
-  <si>
-    <t>VERG. QUAD. 3/8ｴｴ (9,52MM)</t>
-  </si>
-  <si>
-    <t>VERG. SEXT. 13/16ｨ (20,64MM)</t>
-  </si>
-  <si>
-    <t>BARRA CHATA LATAO 3/4 X 1/4 MEIO DURO</t>
-  </si>
-  <si>
-    <t>BARRA RETANGULAR LATAO 1.1/4 (31,75)MM X 1/4 (6,3</t>
-  </si>
-  <si>
-    <t>PROTETOR AURICULAR PLUG C.A 18.189</t>
-  </si>
-  <si>
-    <t>BOTA MARLUVAS COURO NOBUCK 50B26 Nｺ37</t>
-  </si>
-  <si>
-    <t>BOTA MARLUVAS COURO NOBUCK 50B26 Nｺ42</t>
-  </si>
-  <si>
-    <t>PANO DE CHAO</t>
-  </si>
-  <si>
-    <t>DESINFETANTE 2L VOREL LAVANDA START</t>
-  </si>
-  <si>
-    <t>RODO PLASTICO 40CM</t>
-  </si>
-  <si>
-    <t>CABO MADEIRA 1,50M DSR C/ ROSCA</t>
-  </si>
-  <si>
-    <t>LIMPA PISOS DESTAC LAMINADOS FLORES CAMPO E LAVAN</t>
-  </si>
-  <si>
-    <t>ACUCAR UNIAO PCT 01 KG</t>
-  </si>
-  <si>
-    <t>LUVA CIRURGICA DE LATEX TAM. G CX C/ 100 UNID.</t>
-  </si>
-  <si>
-    <t>ENCARTE BLISTER 509 1.1/2 C90/BK90</t>
-  </si>
-  <si>
-    <t>MANUAL ACABAM. 509 3/4 90 / 509 1.1/2 90 LINHA EV</t>
-  </si>
-  <si>
-    <t>SACO TRANSPARENTE 20 X 30 CM 0,06 ESPESSURA</t>
-  </si>
-  <si>
-    <t>SACO TRANSPARENTE 15 X 20 CM</t>
-  </si>
-  <si>
-    <t>PLASTICO BOLHA LARGURA 1,30 MTS</t>
-  </si>
-  <si>
-    <t>SACO LIXO PLASTICO PRETO 100 LTS PCT 5 KG</t>
-  </si>
-  <si>
-    <t>SACO LIXO PT 20LTS C/100 BRAX</t>
-  </si>
-  <si>
-    <t>1370 BOTAO C/SELO (COD TDG 1374) 144 HORAS</t>
-  </si>
-  <si>
-    <t>1107CR PORCA 3/4ｨ CROMADA SALT SPRAY 144 HORAS</t>
+    <t>TUBO 6256 C370 - SUBMONTAGEM</t>
+  </si>
+  <si>
+    <t>TUBO 6256 C620 - SUBMONTAGEM</t>
+  </si>
+  <si>
+    <t>TUBO 2195 C40</t>
+  </si>
+  <si>
+    <t>TUBO 1258 C40</t>
+  </si>
+  <si>
+    <t>TUBO SAIDA 2 X 30CM</t>
+  </si>
+  <si>
+    <t>TUBO 1166 C95</t>
+  </si>
+  <si>
+    <t>TUBO 1169 C95</t>
+  </si>
+  <si>
+    <t>TUBO 1195 C260</t>
+  </si>
+  <si>
+    <t>TUBO 1195 C50</t>
+  </si>
+  <si>
+    <t>TUBO 1195 LR90</t>
+  </si>
+  <si>
+    <t>TUBO 1199 C260</t>
+  </si>
+  <si>
+    <t>TUBO 1199 C95</t>
+  </si>
+  <si>
+    <t>TUBO 1208 LR90</t>
+  </si>
+  <si>
+    <t>TUBO 1209 C95</t>
+  </si>
+  <si>
+    <t>TUBO 1210 C95</t>
+  </si>
+  <si>
+    <t>TUBO 1258 C60</t>
+  </si>
+  <si>
+    <t>TUBO 1865 C350</t>
+  </si>
+  <si>
+    <t>TUBO 1877 C180</t>
+  </si>
+  <si>
+    <t>TUBO SIFAO 88</t>
+  </si>
+  <si>
+    <t>TUBO LIGACAO 1967</t>
+  </si>
+  <si>
+    <t>TUBO SAIDA 11/2 30CM</t>
+  </si>
+  <si>
+    <t>TUBO 1880 C380</t>
+  </si>
+  <si>
+    <t>TUBO 4500 C220</t>
+  </si>
+  <si>
+    <t>TUBO 1168 C42</t>
+  </si>
+  <si>
+    <t>TUBO 1195 C42</t>
+  </si>
+  <si>
+    <t>TUBO 2168 C50</t>
+  </si>
+  <si>
+    <t>TUBO 3000 C60</t>
+  </si>
+  <si>
+    <t>TUBO 3300 C60</t>
+  </si>
+  <si>
+    <t>TUBO 3000 C120</t>
+  </si>
+  <si>
+    <t>TUBO 3100 C120</t>
+  </si>
+  <si>
+    <t>TUBO 3150 C120</t>
+  </si>
+  <si>
+    <t>TUBO 3200 C120</t>
+  </si>
+  <si>
+    <t>TUBO 3300 C120</t>
+  </si>
+  <si>
+    <t>TUBO 3600</t>
+  </si>
+  <si>
+    <t>TUBO ENTRADA 11/2X11/2</t>
+  </si>
+  <si>
+    <t>TUBO ENTRADA 11/2X30CM</t>
+  </si>
+  <si>
+    <t>TUBO ENTRADA 11/4X11/2</t>
+  </si>
+  <si>
+    <t>TUBO ENTRADA 1X11/2</t>
+  </si>
+  <si>
+    <t>TUBO 1166 C105</t>
+  </si>
+  <si>
+    <t>TUBO 1195 C105</t>
+  </si>
+  <si>
+    <t>TUBO 1199 C105</t>
+  </si>
+  <si>
+    <t>TUBO 1208 C105</t>
+  </si>
+  <si>
+    <t>TUBO 1209 C105</t>
+  </si>
+  <si>
+    <t>TUBO 1199 C210</t>
+  </si>
+  <si>
+    <t>TUBO 1256 C210</t>
+  </si>
+  <si>
+    <t>TUBO 1877 C260</t>
+  </si>
+  <si>
+    <t>TUBO 1878 C260</t>
+  </si>
+  <si>
+    <t>TUBO 6195 C95</t>
+  </si>
+  <si>
+    <t>TUBO 6208 C95</t>
+  </si>
+  <si>
+    <t>TUBO 6209 C95</t>
+  </si>
+  <si>
+    <t>TUBO SPUD 1968</t>
+  </si>
+  <si>
+    <t>BARRA 4300 C120</t>
+  </si>
+  <si>
+    <t>BARRA 4400 C120</t>
+  </si>
+  <si>
+    <t>BARRA 4410 C120</t>
+  </si>
+  <si>
+    <t>BARRA 4420 C120</t>
+  </si>
+  <si>
+    <t>BRACO 3000 C350</t>
+  </si>
+  <si>
+    <t>BRACO 3100 C60</t>
+  </si>
+  <si>
+    <t>BRACO 3150 C60</t>
+  </si>
+  <si>
+    <t>BRACO 3200 C60</t>
+  </si>
+  <si>
+    <t>BRACO 3300 C350</t>
+  </si>
+  <si>
+    <t>TUBO 1877 C420</t>
+  </si>
+  <si>
+    <t>BICA 1877 C250</t>
+  </si>
+  <si>
+    <t>BICA 1195 C210</t>
+  </si>
+  <si>
+    <t>BICA 1256 C 220</t>
+  </si>
+  <si>
+    <t>BICA 1877 480</t>
+  </si>
+  <si>
+    <t>BICA 1192 - 290</t>
+  </si>
+  <si>
+    <t>TUBINHO BIDE</t>
+  </si>
+  <si>
+    <t>TUBINHO CACHIMB</t>
+  </si>
+  <si>
+    <t>TUBINHO FLEXIVE</t>
+  </si>
+  <si>
+    <t>BICA 1182 LINHA 800</t>
+  </si>
+  <si>
+    <t>BICA 1181 LINHA 800</t>
+  </si>
+  <si>
+    <t>BICA 1187 LINHA 800</t>
+  </si>
+  <si>
+    <t>BICA 1186 LINHA 800</t>
+  </si>
+  <si>
+    <t>BICA CURTA 1184 LINHA 800</t>
+  </si>
+  <si>
+    <t>BICA LONGA 1183 LINHA 800</t>
+  </si>
+  <si>
+    <t>BICA 1877 C250 (1,10MM PAREDE)</t>
+  </si>
+  <si>
+    <t>BICA 1195 C210 (1,10MM PAREDE)</t>
+  </si>
+  <si>
+    <t>BICA 1168 C/ AREJADOR MOVEL C-42 (REF.3256)</t>
+  </si>
+  <si>
+    <t>BICA 1195 C-42 (REF. 2656)</t>
+  </si>
+  <si>
+    <t>BICA 1208 C210</t>
+  </si>
+  <si>
+    <t>BICA 1209 C210</t>
+  </si>
+  <si>
+    <t>CORPO 1195 480 - SUBMONTAGEM</t>
+  </si>
+  <si>
+    <t>TUBO 1208 C250 - SUBMONTAGEM</t>
+  </si>
+  <si>
+    <t>TUBO 1209 C210 - SUBMONTAGEM</t>
+  </si>
+  <si>
+    <t>TORRE 4400 C48</t>
+  </si>
+  <si>
+    <t>TORRE 4400 C220</t>
+  </si>
+  <si>
+    <t>TORRE 4500 C220</t>
+  </si>
+  <si>
+    <t>TORRE 4610 C220</t>
+  </si>
+  <si>
+    <t>TORRE 4900 C220 DIREITO</t>
+  </si>
+  <si>
+    <t>TORRE 4900 C220 ESQUERDO</t>
+  </si>
+  <si>
+    <t>TORRE 4500 C48</t>
+  </si>
+  <si>
+    <t>TORRE 4900 C48 DIREITO</t>
+  </si>
+  <si>
+    <t>TORRE 4900 C48 ESQUERDO</t>
+  </si>
+  <si>
+    <t>TUBINHO DO MISTURADOR</t>
+  </si>
+  <si>
+    <t>TUBO DE LIGACAO 1967</t>
+  </si>
+  <si>
+    <t>TUBO 1195 C185</t>
+  </si>
+  <si>
+    <t>TUBO 1208 185</t>
+  </si>
+  <si>
+    <t>BRACO1998</t>
+  </si>
+  <si>
+    <t>TUBO 1208 C420</t>
+  </si>
+  <si>
+    <t>TUBO 1207 C420</t>
+  </si>
+  <si>
+    <t>TUBO 1256 C370</t>
+  </si>
+  <si>
+    <t>TUBO 1191 290 HORIZONTAL</t>
+  </si>
+  <si>
+    <t>TUBO 1191 290 VERTICAL SUPERIOR</t>
+  </si>
+  <si>
+    <t>TUBO 290</t>
+  </si>
+  <si>
+    <t>TUBO 1195 C420</t>
+  </si>
+  <si>
+    <t>TUBO SAIDA 2¨ 40CM</t>
+  </si>
+  <si>
+    <t>TUBO ENTRADA 11/2X11/2 30CM ESPECIAL</t>
+  </si>
+  <si>
+    <t>TUBO HASTE 6280 830</t>
+  </si>
+  <si>
+    <t>TUBO CANOPLA 6280 830</t>
+  </si>
+  <si>
+    <t>TUBO 3/4</t>
+  </si>
+  <si>
+    <t>TUBO 5/8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -226,37 +417,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -267,10 +457,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -308,71 +498,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -400,7 +590,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -423,11 +613,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -436,13 +626,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -452,7 +642,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -461,7 +651,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -470,7 +660,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -478,10 +668,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -546,20 +736,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D116"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="13.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="52.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.109375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,642 +763,642 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4">
-        <v>3107</v>
+        <v>5715</v>
       </c>
       <c r="C2" s="1">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+    <row r="3" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4">
-        <v>5271</v>
+        <v>5716</v>
       </c>
       <c r="C3" s="1">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4">
-        <v>5789</v>
+        <v>5719</v>
       </c>
       <c r="C4" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4">
-        <v>5794</v>
+        <v>5720</v>
       </c>
       <c r="C5" s="1">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4">
-        <v>5910</v>
+        <v>5721</v>
       </c>
       <c r="C6" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4">
-        <v>5963</v>
+        <v>5730</v>
       </c>
       <c r="C7" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4">
-        <v>5964</v>
+        <v>5731</v>
       </c>
       <c r="C8" s="1">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" s="4">
-        <v>58745</v>
+        <v>5732</v>
       </c>
       <c r="C9" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
+    <row r="10" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>930</v>
+        <v>5733</v>
       </c>
       <c r="C10" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
+    <row r="11" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
-        <v>1014</v>
+        <v>5734</v>
       </c>
       <c r="C11" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
+    <row r="12" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>1614</v>
+        <v>5735</v>
       </c>
       <c r="C12" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4">
-        <v>25215</v>
+        <v>5736</v>
       </c>
       <c r="C13" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>28405</v>
+        <v>5737</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4">
-        <v>28406</v>
+        <v>5738</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4">
-        <v>1113</v>
+        <v>5739</v>
       </c>
       <c r="C16" s="1">
-        <v>5000</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B17" s="4">
-        <v>3976</v>
+        <v>5740</v>
       </c>
       <c r="C17" s="1">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B18" s="4">
-        <v>5306</v>
+        <v>5741</v>
       </c>
       <c r="C18" s="1">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B19" s="4">
-        <v>5245</v>
+        <v>5742</v>
       </c>
       <c r="C19" s="1">
-        <v>1500</v>
+        <v>10</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B20" s="4">
-        <v>5305</v>
+        <v>5743</v>
       </c>
       <c r="C20" s="1">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B21" s="4">
-        <v>2348</v>
+        <v>5744</v>
       </c>
       <c r="C21" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21.75">
+    <row r="22" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B22" s="4">
-        <v>2446</v>
+        <v>5745</v>
       </c>
       <c r="C22" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="21.75">
+    <row r="23" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B23" s="4">
-        <v>2606</v>
+        <v>5748</v>
       </c>
       <c r="C23" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="21.75">
+    <row r="24" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B24" s="4">
-        <v>2678</v>
+        <v>5749</v>
       </c>
       <c r="C24" s="1">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B25" s="4">
-        <v>2704</v>
+        <v>5751</v>
       </c>
       <c r="C25" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B26" s="4">
-        <v>2838</v>
+        <v>5752</v>
       </c>
       <c r="C26" s="1">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B27" s="4">
-        <v>2863</v>
+        <v>5753</v>
       </c>
       <c r="C27" s="1">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B28" s="4">
-        <v>2912</v>
+        <v>5754</v>
       </c>
       <c r="C28" s="1">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B29" s="4">
-        <v>2961</v>
+        <v>5755</v>
       </c>
       <c r="C29" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B30" s="4">
-        <v>3039</v>
+        <v>5765</v>
       </c>
       <c r="C30" s="1">
-        <v>1500</v>
+        <v>10</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B31" s="4">
-        <v>3036</v>
+        <v>5766</v>
       </c>
       <c r="C31" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B32" s="4">
-        <v>11</v>
+        <v>5767</v>
       </c>
       <c r="C32" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B33" s="4">
-        <v>260</v>
+        <v>5768</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B34" s="4">
-        <v>266</v>
+        <v>5769</v>
       </c>
       <c r="C34" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B35" s="4">
-        <v>35</v>
+        <v>5770</v>
       </c>
       <c r="C35" s="1">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B36" s="4">
-        <v>59</v>
+        <v>5775</v>
       </c>
       <c r="C36" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B37" s="4">
-        <v>342</v>
+        <v>5776</v>
       </c>
       <c r="C37" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B38" s="4">
-        <v>758</v>
+        <v>5777</v>
       </c>
       <c r="C38" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B39" s="4">
-        <v>771</v>
+        <v>5778</v>
       </c>
       <c r="C39" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B40" s="4">
-        <v>2148</v>
+        <v>5785</v>
       </c>
       <c r="C40" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>13</v>
       </c>
       <c r="B41" s="4">
-        <v>5173</v>
+        <v>5786</v>
       </c>
       <c r="C41" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B42" s="4">
-        <v>6148</v>
+        <v>5787</v>
       </c>
       <c r="C42" s="1">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B43" s="4">
-        <v>6149</v>
+        <v>5788</v>
       </c>
       <c r="C43" s="1">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B44" s="4">
-        <v>2128</v>
+        <v>5789</v>
       </c>
       <c r="C44" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B45" s="4">
-        <v>2139</v>
+        <v>5791</v>
       </c>
       <c r="C45" s="1">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B46" s="4">
-        <v>3034</v>
+        <v>5793</v>
       </c>
       <c r="C46" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B47" s="4">
-        <v>11</v>
+        <v>5800</v>
       </c>
       <c r="C47" s="1">
         <v>10</v>
@@ -1217,12 +1407,12 @@
         <v>49</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B48" s="4">
-        <v>751</v>
+        <v>5801</v>
       </c>
       <c r="C48" s="1">
         <v>10</v>
@@ -1231,35 +1421,960 @@
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B49" s="4">
-        <v>452</v>
+        <v>5802</v>
       </c>
       <c r="C49" s="1">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B50" s="4">
-        <v>1541</v>
+        <v>5803</v>
       </c>
       <c r="C50" s="1">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>52</v>
       </c>
     </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
+        <v>13</v>
+      </c>
+      <c r="B51" s="6">
+        <v>5804</v>
+      </c>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
+        <v>13</v>
+      </c>
+      <c r="B52" s="6">
+        <v>5806</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="5">
+        <v>13</v>
+      </c>
+      <c r="B53" s="6">
+        <v>5756</v>
+      </c>
+      <c r="C53" s="1">
+        <v>10</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
+        <v>13</v>
+      </c>
+      <c r="B54" s="6">
+        <v>5757</v>
+      </c>
+      <c r="C54" s="1">
+        <v>10</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="5">
+        <v>13</v>
+      </c>
+      <c r="B55" s="6">
+        <v>5758</v>
+      </c>
+      <c r="C55" s="1">
+        <v>10</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
+        <v>13</v>
+      </c>
+      <c r="B56" s="6">
+        <v>5759</v>
+      </c>
+      <c r="C56" s="1">
+        <v>10</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="5">
+        <v>13</v>
+      </c>
+      <c r="B57" s="6">
+        <v>5795</v>
+      </c>
+      <c r="C57" s="1">
+        <v>10</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
+        <v>13</v>
+      </c>
+      <c r="B58" s="6">
+        <v>5796</v>
+      </c>
+      <c r="C58" s="1">
+        <v>10</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="5">
+        <v>13</v>
+      </c>
+      <c r="B59" s="6">
+        <v>5797</v>
+      </c>
+      <c r="C59" s="1">
+        <v>10</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
+        <v>13</v>
+      </c>
+      <c r="B60" s="6">
+        <v>5798</v>
+      </c>
+      <c r="C60" s="1">
+        <v>10</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="5">
+        <v>13</v>
+      </c>
+      <c r="B61" s="6">
+        <v>5799</v>
+      </c>
+      <c r="C61" s="1">
+        <v>10</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
+        <v>13</v>
+      </c>
+      <c r="B62" s="6">
+        <v>48361</v>
+      </c>
+      <c r="C62" s="1">
+        <v>10</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="5">
+        <v>13</v>
+      </c>
+      <c r="B63" s="6">
+        <v>5258</v>
+      </c>
+      <c r="C63" s="1">
+        <v>10</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
+        <v>13</v>
+      </c>
+      <c r="B64" s="6">
+        <v>5259</v>
+      </c>
+      <c r="C64" s="1">
+        <v>10</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="5">
+        <v>13</v>
+      </c>
+      <c r="B65" s="6">
+        <v>5306</v>
+      </c>
+      <c r="C65" s="1">
+        <v>10</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="5">
+        <v>13</v>
+      </c>
+      <c r="B66" s="6">
+        <v>5602</v>
+      </c>
+      <c r="C66" s="1">
+        <v>10</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="5">
+        <v>13</v>
+      </c>
+      <c r="B67" s="6">
+        <v>5694</v>
+      </c>
+      <c r="C67" s="1">
+        <v>10</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="5">
+        <v>13</v>
+      </c>
+      <c r="B68" s="6">
+        <v>5729</v>
+      </c>
+      <c r="C68" s="1">
+        <v>10</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="5">
+        <v>13</v>
+      </c>
+      <c r="B69" s="6">
+        <v>5747</v>
+      </c>
+      <c r="C69" s="1">
+        <v>10</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="5">
+        <v>13</v>
+      </c>
+      <c r="B70" s="6">
+        <v>5750</v>
+      </c>
+      <c r="C70" s="1">
+        <v>10</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="5">
+        <v>13</v>
+      </c>
+      <c r="B71" s="6">
+        <v>5672</v>
+      </c>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="5">
+        <v>13</v>
+      </c>
+      <c r="B72" s="6">
+        <v>5673</v>
+      </c>
+      <c r="C72" s="1">
+        <v>10</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="5">
+        <v>13</v>
+      </c>
+      <c r="B73" s="6">
+        <v>5674</v>
+      </c>
+      <c r="C73" s="1">
+        <v>10</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="5">
+        <v>13</v>
+      </c>
+      <c r="B74" s="6">
+        <v>5675</v>
+      </c>
+      <c r="C74" s="1">
+        <v>10</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="5">
+        <v>13</v>
+      </c>
+      <c r="B75" s="6">
+        <v>5688</v>
+      </c>
+      <c r="C75" s="1">
+        <v>10</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="5">
+        <v>13</v>
+      </c>
+      <c r="B76" s="6">
+        <v>5689</v>
+      </c>
+      <c r="C76" s="1">
+        <v>10</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="5">
+        <v>13</v>
+      </c>
+      <c r="B77" s="6">
+        <v>5258</v>
+      </c>
+      <c r="C77" s="1">
+        <v>10</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="5">
+        <v>13</v>
+      </c>
+      <c r="B78" s="6">
+        <v>5259</v>
+      </c>
+      <c r="C78" s="1">
+        <v>10</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="5">
+        <v>13</v>
+      </c>
+      <c r="B79" s="6">
+        <v>5445</v>
+      </c>
+      <c r="C79" s="1">
+        <v>10</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="5">
+        <v>13</v>
+      </c>
+      <c r="B80" s="6">
+        <v>5446</v>
+      </c>
+      <c r="C80" s="1">
+        <v>10</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="5">
+        <v>13</v>
+      </c>
+      <c r="B81" s="6">
+        <v>5512</v>
+      </c>
+      <c r="C81" s="1">
+        <v>10</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="5">
+        <v>13</v>
+      </c>
+      <c r="B82" s="6">
+        <v>5513</v>
+      </c>
+      <c r="C82" s="1">
+        <v>10</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="5">
+        <v>13</v>
+      </c>
+      <c r="B83" s="6">
+        <v>5602</v>
+      </c>
+      <c r="C83" s="1">
+        <v>10</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="5">
+        <v>13</v>
+      </c>
+      <c r="B84" s="6">
+        <v>5830</v>
+      </c>
+      <c r="C84" s="1">
+        <v>10</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="5">
+        <v>13</v>
+      </c>
+      <c r="B85" s="6">
+        <v>5513</v>
+      </c>
+      <c r="C85" s="1">
+        <v>10</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="5">
+        <v>13</v>
+      </c>
+      <c r="B86" s="6">
+        <v>5771</v>
+      </c>
+      <c r="C86" s="1">
+        <v>10</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="5">
+        <v>13</v>
+      </c>
+      <c r="B87" s="6">
+        <v>5760</v>
+      </c>
+      <c r="C87" s="1">
+        <v>10</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="5">
+        <v>13</v>
+      </c>
+      <c r="B88" s="6">
+        <v>5761</v>
+      </c>
+      <c r="C88" s="1">
+        <v>10</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="5">
+        <v>13</v>
+      </c>
+      <c r="B89" s="6">
+        <v>5762</v>
+      </c>
+      <c r="C89" s="1">
+        <v>10</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="5">
+        <v>13</v>
+      </c>
+      <c r="B90" s="6">
+        <v>5763</v>
+      </c>
+      <c r="C90" s="1">
+        <v>10</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="5">
+        <v>13</v>
+      </c>
+      <c r="B91" s="6">
+        <v>5764</v>
+      </c>
+      <c r="C91" s="1">
+        <v>10</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="5">
+        <v>13</v>
+      </c>
+      <c r="B92" s="6">
+        <v>5772</v>
+      </c>
+      <c r="C92" s="1">
+        <v>10</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="5">
+        <v>13</v>
+      </c>
+      <c r="B93" s="6">
+        <v>5773</v>
+      </c>
+      <c r="C93" s="1">
+        <v>10</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="5">
+        <v>13</v>
+      </c>
+      <c r="B94" s="6">
+        <v>5774</v>
+      </c>
+      <c r="C94" s="1">
+        <v>10</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="5">
+        <v>13</v>
+      </c>
+      <c r="B95" s="6">
+        <v>5756</v>
+      </c>
+      <c r="C95" s="1">
+        <v>10</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="5">
+        <v>13</v>
+      </c>
+      <c r="B96" s="6">
+        <v>5758</v>
+      </c>
+      <c r="C96" s="1">
+        <v>10</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="5">
+        <v>13</v>
+      </c>
+      <c r="B97" s="6">
+        <v>5759</v>
+      </c>
+      <c r="C97" s="1">
+        <v>10</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="5">
+        <v>13</v>
+      </c>
+      <c r="B98" s="6">
+        <v>5823</v>
+      </c>
+      <c r="C98" s="1">
+        <v>10</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="5">
+        <v>13</v>
+      </c>
+      <c r="B99" s="6">
+        <v>5744</v>
+      </c>
+      <c r="C99" s="1">
+        <v>10</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="5">
+        <v>13</v>
+      </c>
+      <c r="B100" s="6">
+        <v>5819</v>
+      </c>
+      <c r="C100" s="1">
+        <v>10</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="5">
+        <v>13</v>
+      </c>
+      <c r="B101" s="6">
+        <v>5818</v>
+      </c>
+      <c r="C101" s="1">
+        <v>10</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="5">
+        <v>13</v>
+      </c>
+      <c r="B102" s="6">
+        <v>5821</v>
+      </c>
+      <c r="C102" s="1">
+        <v>10</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="5">
+        <v>13</v>
+      </c>
+      <c r="B103" s="6">
+        <v>5822</v>
+      </c>
+      <c r="C103" s="1">
+        <v>10</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="5">
+        <v>13</v>
+      </c>
+      <c r="B104" s="6">
+        <v>5783</v>
+      </c>
+      <c r="C104" s="1">
+        <v>10</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="5">
+        <v>13</v>
+      </c>
+      <c r="B105" s="6">
+        <v>5768</v>
+      </c>
+      <c r="C105" s="1">
+        <v>10</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="5">
+        <v>13</v>
+      </c>
+      <c r="B106" s="6">
+        <v>6395</v>
+      </c>
+      <c r="C106" s="1">
+        <v>10</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="5">
+        <v>13</v>
+      </c>
+      <c r="B107" s="6">
+        <v>6396</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="5">
+        <v>13</v>
+      </c>
+      <c r="B108" s="6">
+        <v>5837</v>
+      </c>
+      <c r="C108" s="1">
+        <v>10</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="5">
+        <v>13</v>
+      </c>
+      <c r="B109" s="6">
+        <v>5835</v>
+      </c>
+      <c r="C109" s="1">
+        <v>10</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="5">
+        <v>13</v>
+      </c>
+      <c r="B110" s="6">
+        <v>6397</v>
+      </c>
+      <c r="C110" s="1">
+        <v>10</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="5">
+        <v>13</v>
+      </c>
+      <c r="B111" s="6">
+        <v>48362</v>
+      </c>
+      <c r="C111" s="5">
+        <v>10</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="5">
+        <v>13</v>
+      </c>
+      <c r="B112" s="6">
+        <v>6398</v>
+      </c>
+      <c r="C112" s="5">
+        <v>10</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="5">
+        <v>13</v>
+      </c>
+      <c r="B113" s="6">
+        <v>6376</v>
+      </c>
+      <c r="C113" s="5">
+        <v>10</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="5">
+        <v>13</v>
+      </c>
+      <c r="B114" s="6">
+        <v>6377</v>
+      </c>
+      <c r="C114" s="5">
+        <v>10</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="5">
+        <v>3</v>
+      </c>
+      <c r="B115" s="6">
+        <v>2214</v>
+      </c>
+      <c r="C115" s="5">
+        <v>10</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="5">
+        <v>3</v>
+      </c>
+      <c r="B116" s="6">
+        <v>2275</v>
+      </c>
+      <c r="C116" s="5">
+        <v>10</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>